--- a/data/TTS/最新版班表/2026-10/TTS_TD.xlsx
+++ b/data/TTS/最新版班表/2026-10/TTS_TD.xlsx
@@ -1584,36 +1584,24 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="N10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1621,28 +1609,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U10" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1864,12 +1843,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W11" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1931,12 +1907,9 @@
           <t>李芝妍</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2003,28 +1976,19 @@
 9:40</t>
         </is>
       </c>
-      <c r="M12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2032,12 +1996,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q12" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -2301,12 +2262,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2314,28 +2272,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC13" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2448,28 +2397,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="P14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2477,28 +2417,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="T14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2511,36 +2442,24 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Z14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB14" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2884,12 +2803,9 @@
 8:15</t>
         </is>
       </c>
-      <c r="S16" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2923,12 +2839,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2941,28 +2854,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD16" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -2977,20 +2881,14 @@
           <t>陳耀邦</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3070,20 +2968,14 @@
 8:23</t>
         </is>
       </c>
-      <c r="P17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q17" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -3260,12 +3152,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="N18" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -3958,12 +3847,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W21" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X21" s="1" t="inlineStr">
@@ -4215,20 +4101,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AC22" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AD22" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -4332,12 +4212,9 @@
 8:02</t>
         </is>
       </c>
-      <c r="P23" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Q23" s="1" t="inlineStr">
@@ -4356,12 +4233,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="S23" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4470,20 +4344,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -5047,12 +4915,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AB26" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="AC26" s="1" t="inlineStr">
@@ -5603,12 +5468,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -5645,12 +5507,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -5658,12 +5517,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y29" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="Z29" s="1" t="inlineStr">
@@ -5712,12 +5568,9 @@
           <t>洪健森</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5759,12 +5612,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -5988,12 +5838,9 @@
 9:45</t>
         </is>
       </c>
-      <c r="L31" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -6185,20 +6032,14 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -6272,12 +6113,9 @@
 9:15</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -6459,12 +6297,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S33" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T33" s="1" t="inlineStr">
@@ -6580,12 +6415,9 @@
 9:40</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
@@ -6660,20 +6492,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="S34" s="1" t="inlineStr">
@@ -6724,20 +6550,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA34" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="AB34" s="1" t="inlineStr">
@@ -6934,36 +6754,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z35" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA35" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB35" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC35" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -7001,12 +6809,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
@@ -7035,36 +6840,24 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L36" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M36" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N36" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -7336,12 +7129,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -7349,12 +7139,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="Y37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-CMP
-17:30
-8:00</t>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>CMP</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -7362,20 +7149,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="AA37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -7383,12 +7164,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD37" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7245,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L38" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M38" s="1" t="inlineStr">
@@ -7630,20 +7405,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -8323,12 +8092,9 @@
 9:50</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -8399,12 +8165,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="W42" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -8953,12 +8716,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M45" s="1" t="inlineStr">
@@ -9398,36 +9158,24 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="R47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -9440,20 +9188,14 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="U47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V47" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="W47" s="1" t="inlineStr">
@@ -10445,12 +10187,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="L52" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="M52" s="1" t="inlineStr">
@@ -10559,12 +10298,9 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB52" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="AC52" s="1" t="inlineStr">
@@ -10629,12 +10365,9 @@
 8:40</t>
         </is>
       </c>
-      <c r="H53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -10647,28 +10380,19 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="M53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -10676,28 +10400,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="O53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="P53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="Q53" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -10705,12 +10420,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S53" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T53" s="1" t="inlineStr">
@@ -10903,12 +10615,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q54" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr">
@@ -11482,12 +11191,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I57" s="1" t="inlineStr">
@@ -11575,12 +11281,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="V57" s="1" t="inlineStr">
@@ -11674,20 +11377,14 @@
 9:40</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -11705,12 +11402,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -11819,20 +11513,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="Z58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AA58" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>DTT</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="AB58" s="1" t="inlineStr">
@@ -12034,28 +11722,19 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AA59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AB59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC59" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="AD59" s="1" t="inlineStr">
@@ -12498,20 +12177,14 @@
           <t>許凱安</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -12855,12 +12528,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="W63" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X63" s="1" t="inlineStr">
@@ -13258,12 +12928,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="T65" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="U65" s="1" t="inlineStr">
@@ -13449,12 +13116,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R66" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S66" s="1" t="inlineStr">
@@ -14301,12 +13965,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="R70" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUTS
-17:30
-8:00</t>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>LUTS</t>
         </is>
       </c>
       <c r="S70" s="1" t="inlineStr">
@@ -14730,12 +14391,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="S72" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-DTT
-17:30
-8:00</t>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>DTT</t>
         </is>
       </c>
       <c r="T72" s="1" t="inlineStr">
@@ -14939,12 +14597,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="S73" s="1" t="inlineStr">
-        <is>
-          <t>7:30
-TOWN
-16:30
-8:00</t>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>TOWN</t>
         </is>
       </c>
       <c r="T73" s="1" t="inlineStr">
@@ -15052,20 +14707,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="F74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -15092,12 +14741,9 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="L74" s="1" t="inlineStr">
@@ -15108,28 +14754,19 @@
 8:00</t>
         </is>
       </c>
-      <c r="M74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="N74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="O74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -15147,44 +14784,29 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="S74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="T74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="U74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="V74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="W74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -15213,20 +14835,14 @@
 8:00</t>
         </is>
       </c>
-      <c r="AB74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="AC74" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-LUT
-17:30
-8:00</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>LUT</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>LUT</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -15490,12 +15106,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="H76" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -15503,12 +15116,9 @@
           <t>DO2</t>
         </is>
       </c>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -16188,12 +15798,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="Q79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="R79" s="1" t="inlineStr">
@@ -16277,12 +15884,9 @@
           <t>DO3X</t>
         </is>
       </c>
-      <c r="AD79" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-FAC
-17:30
-8:00</t>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>FAC</t>
         </is>
       </c>
     </row>
@@ -16297,12 +15901,9 @@
           <t>林承正</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16353,20 +15954,14 @@
           <t>DO1</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>8:30
-PAY
-17:30
-8:00</t>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>PAY</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>PAY</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
